--- a/sales-sample/中小企業決裁者リスト_業種別収集キット_20260820.xlsx
+++ b/sales-sample/中小企業決裁者リスト_業種別収集キット_20260820.xlsx
@@ -1490,7 +1490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P6"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1675,22 +1675,938 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>2026/8/20</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>IT・Web制作・システム開発</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>東京都→福岡</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>sogitani / baigie inc.</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>@sogitani_baigie</t>
+        </is>
+      </c>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>https://x.com/sogitani_baigie</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>株式会社ベイジ 代表取締役</t>
+        </is>
+      </c>
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>株式会社ベイジ</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
+        <is>
+          <t>約10.4万</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>要最終確認</t>
+        </is>
+      </c>
+      <c r="M3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N3" s="5" t="inlineStr">
+        <is>
+          <t>Web検索(Claude)</t>
+        </is>
+      </c>
+      <c r="O3" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="inlineStr">
+        <is>
+          <t>BtoB向けWeb制作。経営者Twitter論の発信でも著名</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="A4" s="12" t="inlineStr">
-        <is>
-          <t>検証レベルの定義: A=アカウント実在＋会社の実在を公的DBで確認済み ／ B=アカウント実在は目視確認済み（会社は未照合） ／ C=Grok出力のまま（未検証・納品物に含めない）</t>
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>2026/8/20</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>IT・Web制作・システム開発</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>けんすう</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>@kensuu</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>https://x.com/kensuu</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>アル株式会社 代表取締役</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>アル株式会社</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>要最終確認</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
+          <t>Web検索(Claude)</t>
+        </is>
+      </c>
+      <c r="O4" s="3" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>Webサービス・NFT。発信量が非常に多い</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="12" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>2026/8/20</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>IT・Web制作・システム開発</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>辻正浩 | Masahiro Tsuji</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>@tsuj</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>https://x.com/tsuj</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>株式会社so.la 代表取締役</t>
+        </is>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>株式会社so.la</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>約4.2万</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L5" s="5" t="inlineStr">
+        <is>
+          <t>要最終確認</t>
+        </is>
+      </c>
+      <c r="M5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N5" s="5" t="inlineStr">
+        <is>
+          <t>Web検索(Claude)</t>
+        </is>
+      </c>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="inlineStr">
+        <is>
+          <t>SEO専門。2025年1月にFaber Company（上場）グループ入り</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>2026/8/20</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>広告・マーケ・デザイン</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>栗原 康太 | 才流（サイル）</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>@kotakurihara</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>https://x.com/kotakurihara</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>株式会社才流 代表取締役</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>株式会社才流</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>要最終確認</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
+          <t>Web検索(Claude)</t>
+        </is>
+      </c>
+      <c r="O6" s="3" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>BtoBマーケ支援コンサル</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>2026/8/20</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>広告・マーケ・デザイン</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>三浦崇宏 GO</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>@TAKAHIRO3IURA</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>https://x.com/TAKAHIRO3IURA</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>The Breakthrough Company GO 代表</t>
+        </is>
+      </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>株式会社GO</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L7" s="5" t="inlineStr">
+        <is>
+          <t>要最終確認</t>
+        </is>
+      </c>
+      <c r="M7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N7" s="5" t="inlineStr">
+        <is>
+          <t>Web検索(Claude)</t>
+        </is>
+      </c>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="inlineStr">
+        <is>
+          <t>クリエイティブ・広告</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>2026/8/20</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>広告・マーケ・デザイン</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>明石ガクト / ONE MEDIA</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>@gakuto_akashi</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>https://x.com/gakuto_akashi</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>ワンメディア株式会社 代表取締役CEO</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>ワンメディア株式会社</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>要最終確認</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t>Web検索(Claude)</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>ショート動画マーケ・SNSプロモーション</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>2026/8/20</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>広告・マーケ・デザイン</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>佐藤ねじ / ブルーパドル</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>@sato_nezi</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>https://x.com/sato_nezi</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>株式会社ブルーパドル 代表</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>株式会社ブルーパドル</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>要最終確認</t>
+        </is>
+      </c>
+      <c r="M9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N9" s="5" t="inlineStr">
+        <is>
+          <t>Web検索(Claude)</t>
+        </is>
+      </c>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="P9" s="5" t="inlineStr">
+        <is>
+          <t>小規模の企画・デザイン会社。2025年7月の投稿を確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>2026/8/20</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>広告・マーケ・デザイン</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>関西（要確認）</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>松尾 茂起（ウェブライダー）</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>@seokyoto</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>https://x.com/seokyoto</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>株式会社ウェブライダー 代表取締役</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>株式会社ウェブライダー</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>要最終確認</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
+          <t>Web検索(Claude)</t>
+        </is>
+      </c>
+      <c r="O10" s="3" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>SEO・コンテンツ制作。『沈黙のWebライティング』著者。2025年6月の投稿を確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>2026/8/20</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>教育・塾・スクール</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>大滝昇平｜デイトラ＆にぼし香 代表</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>@showheyohtaki</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>https://x.com/showheyohtaki</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>株式会社デイトラ 代表</t>
+        </is>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>株式会社デイトラ</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>要最終確認</t>
+        </is>
+      </c>
+      <c r="M11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N11" s="5" t="inlineStr">
+        <is>
+          <t>Web検索(Claude)</t>
+        </is>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="P11" s="5" t="inlineStr">
+        <is>
+          <t>Webスキルスクール＋ラーメン店6店舗経営（飲食にも該当）。2026年の投稿を確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>2026/8/20</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>教育・塾・スクール</t>
+        </is>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>池田 朋弘</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>@pop_ikeda</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>https://x.com/pop_ikeda</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>株式会社Workstyle Evolution 代表取締役</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>株式会社Workstyle Evolution</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>要最終確認</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t>Web検索(Claude)</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>AI研修・書籍多数。2026年の投稿を確認</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>2026/8/20</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>士業（税理士・社労士等）</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>東京都</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>大河内薫＠お金の教育</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>@k_art_u</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>https://x.com/k_art_u</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
+        <is>
+          <t>株式会社ArtBiz 代表取締役・ArtBiz税理士事務所 代表税理士</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>株式会社ArtBiz</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>未</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L13" s="5" t="inlineStr">
+        <is>
+          <t>要最終確認</t>
+        </is>
+      </c>
+      <c r="M13" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="N13" s="5" t="inlineStr">
+        <is>
+          <t>Web検索(Claude)</t>
+        </is>
+      </c>
+      <c r="O13" s="5" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="P13" s="5" t="inlineStr">
+        <is>
+          <t>税理士でフォロワー数国内最大級。お金の教育で発信</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>検証レベルの定義: A=アカウント実在＋会社の実在を公的DBで確認済み ／ B=アカウント実在・本人性・会社名をWeb情報で確認済み（法人番号は未照合） ／ C=Grok出力のまま（未検証・納品物に含めない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
         <is>
           <t>黄色の行は記入例（ダミー）。実在のアカウントではありません。実運用開始時に削除してください</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>3行目以降の11件は2026年8月20日にWeb検索で個別検証したデモ実データ（レベルB）。法人番号照合と直近投稿日の最終確認で レベルA に昇格できます</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>注意: Web検索で拾えるのは「発信が有名な経営者」に偏ります。無名層まで量産するのはGrok／X API側の役割（Grokプロンプト集シート参照）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>法人番号照合列: 国税庁法人番号公表サイトで会社名がヒットしたら○。個人事業の場合は「個」と記入</t>
         </is>
